--- a/artfynd/A 34528-2025 artfynd.xlsx
+++ b/artfynd/A 34528-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127814016</v>
       </c>
       <c r="B2" t="n">
-        <v>92658</v>
+        <v>92664</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127813682</v>
       </c>
       <c r="B3" t="n">
-        <v>90832</v>
+        <v>90838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>127813710</v>
       </c>
       <c r="B4" t="n">
-        <v>90832</v>
+        <v>90838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>127813667</v>
       </c>
       <c r="B5" t="n">
-        <v>90832</v>
+        <v>90838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,6 +1148,601 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128064167</v>
+      </c>
+      <c r="B6" t="n">
+        <v>82864</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fridhem (Erken), Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>698438</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6637253</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128064178</v>
+      </c>
+      <c r="B7" t="n">
+        <v>82864</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fridhem (Erken), Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>698423</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6637254</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128064221</v>
+      </c>
+      <c r="B8" t="n">
+        <v>82864</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fridhem (Erken), Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>698433</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6637241</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128064210</v>
+      </c>
+      <c r="B9" t="n">
+        <v>82864</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fridhem (Erken), Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>698425</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6637249</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128064185</v>
+      </c>
+      <c r="B10" t="n">
+        <v>82864</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fridhem (Erken), Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>698427</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6637261</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34528-2025 artfynd.xlsx
+++ b/artfynd/A 34528-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127814016</v>
       </c>
       <c r="B2" t="n">
-        <v>92664</v>
+        <v>92667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127813682</v>
       </c>
       <c r="B3" t="n">
-        <v>90838</v>
+        <v>90841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>127813710</v>
       </c>
       <c r="B4" t="n">
-        <v>90838</v>
+        <v>90841</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>127813667</v>
       </c>
       <c r="B5" t="n">
-        <v>90838</v>
+        <v>90841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128064178</v>
+        <v>128064221</v>
       </c>
       <c r="B7" t="n">
         <v>82864</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698423</v>
+        <v>698433</v>
       </c>
       <c r="R7" t="n">
-        <v>6637254</v>
+        <v>6637241</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128064221</v>
+        <v>128064178</v>
       </c>
       <c r="B8" t="n">
         <v>82864</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698433</v>
+        <v>698423</v>
       </c>
       <c r="R8" t="n">
-        <v>6637241</v>
+        <v>6637254</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 34528-2025 artfynd.xlsx
+++ b/artfynd/A 34528-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127814016</v>
       </c>
       <c r="B2" t="n">
-        <v>92667</v>
+        <v>92675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127813682</v>
       </c>
       <c r="B3" t="n">
-        <v>90841</v>
+        <v>90849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>127813710</v>
       </c>
       <c r="B4" t="n">
-        <v>90841</v>
+        <v>90849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>127813667</v>
       </c>
       <c r="B5" t="n">
-        <v>90841</v>
+        <v>90849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>128064167</v>
       </c>
       <c r="B6" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128064221</v>
       </c>
       <c r="B7" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128064178</v>
       </c>
       <c r="B8" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>128064210</v>
       </c>
       <c r="B9" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>128064185</v>
       </c>
       <c r="B10" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 34528-2025 artfynd.xlsx
+++ b/artfynd/A 34528-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127814016</v>
       </c>
       <c r="B2" t="n">
-        <v>92675</v>
+        <v>92676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127813682</v>
       </c>
       <c r="B3" t="n">
-        <v>90849</v>
+        <v>90850</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>127813710</v>
       </c>
       <c r="B4" t="n">
-        <v>90849</v>
+        <v>90850</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>127813667</v>
       </c>
       <c r="B5" t="n">
-        <v>90849</v>
+        <v>90850</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34528-2025 artfynd.xlsx
+++ b/artfynd/A 34528-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127814016</v>
       </c>
       <c r="B2" t="n">
-        <v>92676</v>
+        <v>92677</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127813682</v>
       </c>
       <c r="B3" t="n">
-        <v>90850</v>
+        <v>90851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>127813710</v>
       </c>
       <c r="B4" t="n">
-        <v>90850</v>
+        <v>90851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>127813667</v>
       </c>
       <c r="B5" t="n">
-        <v>90850</v>
+        <v>90851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34528-2025 artfynd.xlsx
+++ b/artfynd/A 34528-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127814016</v>
       </c>
       <c r="B2" t="n">
-        <v>92677</v>
+        <v>92678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127813682</v>
       </c>
       <c r="B3" t="n">
-        <v>90851</v>
+        <v>90852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>127813710</v>
       </c>
       <c r="B4" t="n">
-        <v>90851</v>
+        <v>90852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>127813667</v>
       </c>
       <c r="B5" t="n">
-        <v>90851</v>
+        <v>90852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34528-2025 artfynd.xlsx
+++ b/artfynd/A 34528-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1744,6 +1744,918 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128346968</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Erken, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>698375</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6637261</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128346802</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90855</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5745</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gyllenfingersvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ramaria brunneicontusa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fridhem Erken, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>698388</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6637237</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128347045</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92290</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Erken, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>698345</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6637238</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128347169</v>
+      </c>
+      <c r="B14" t="n">
+        <v>82872</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Erken , Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>698346</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6637297</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128346963</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92679</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Erken, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>698375</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6637261</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128346779</v>
+      </c>
+      <c r="B16" t="n">
+        <v>82872</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fridhem (Erken), Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>698383</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6637243</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128347159</v>
+      </c>
+      <c r="B17" t="n">
+        <v>82872</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fridhem (Erken), Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>698345</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6637306</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128346773</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90855</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5745</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gyllenfingersvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ramaria brunneicontusa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fridhem (Erken), Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>698383</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6637243</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34528-2025 artfynd.xlsx
+++ b/artfynd/A 34528-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127814016</v>
       </c>
       <c r="B2" t="n">
-        <v>92678</v>
+        <v>92686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127813682</v>
       </c>
       <c r="B3" t="n">
-        <v>90852</v>
+        <v>90858</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>127813710</v>
       </c>
       <c r="B4" t="n">
-        <v>90852</v>
+        <v>90858</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>127813667</v>
       </c>
       <c r="B5" t="n">
-        <v>90852</v>
+        <v>90858</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>128064167</v>
       </c>
       <c r="B6" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128064221</v>
       </c>
       <c r="B7" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128064178</v>
       </c>
       <c r="B8" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>128064210</v>
       </c>
       <c r="B9" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>128064185</v>
       </c>
       <c r="B10" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128346968</v>
       </c>
       <c r="B11" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>128346802</v>
       </c>
       <c r="B12" t="n">
-        <v>90855</v>
+        <v>90858</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>128347045</v>
       </c>
       <c r="B13" t="n">
-        <v>92290</v>
+        <v>92295</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>128347169</v>
       </c>
       <c r="B14" t="n">
-        <v>82872</v>
+        <v>82873</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>128346963</v>
       </c>
       <c r="B15" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>128346779</v>
       </c>
       <c r="B16" t="n">
-        <v>82872</v>
+        <v>82873</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>128347159</v>
       </c>
       <c r="B17" t="n">
-        <v>82872</v>
+        <v>82873</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>128346773</v>
       </c>
       <c r="B18" t="n">
-        <v>90855</v>
+        <v>90858</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 34528-2025 artfynd.xlsx
+++ b/artfynd/A 34528-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127814016</v>
       </c>
       <c r="B2" t="n">
-        <v>92686</v>
+        <v>92778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>127813682</v>
       </c>
       <c r="B3" t="n">
-        <v>90858</v>
+        <v>90950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>127813710</v>
       </c>
       <c r="B4" t="n">
-        <v>90858</v>
+        <v>90950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>127813667</v>
       </c>
       <c r="B5" t="n">
-        <v>90858</v>
+        <v>90950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>128064167</v>
       </c>
       <c r="B6" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128064221</v>
       </c>
       <c r="B7" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128064178</v>
       </c>
       <c r="B8" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>128064210</v>
       </c>
       <c r="B9" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>128064185</v>
       </c>
       <c r="B10" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128346968</v>
       </c>
       <c r="B11" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>128346802</v>
       </c>
       <c r="B12" t="n">
-        <v>90858</v>
+        <v>90950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>128347045</v>
       </c>
       <c r="B13" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>128347169</v>
       </c>
       <c r="B14" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>128346963</v>
       </c>
       <c r="B15" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>128346779</v>
       </c>
       <c r="B16" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>128347159</v>
       </c>
       <c r="B17" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>128346773</v>
       </c>
       <c r="B18" t="n">
-        <v>90858</v>
+        <v>90950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 34528-2025 artfynd.xlsx
+++ b/artfynd/A 34528-2025 artfynd.xlsx
@@ -1154,7 +1154,7 @@
         <v>128064167</v>
       </c>
       <c r="B6" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>128064221</v>
       </c>
       <c r="B7" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128064178</v>
       </c>
       <c r="B8" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>128064210</v>
       </c>
       <c r="B9" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>128064185</v>
       </c>
       <c r="B10" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128346968</v>
       </c>
       <c r="B11" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>128346802</v>
       </c>
       <c r="B12" t="n">
-        <v>90950</v>
+        <v>90962</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>128347045</v>
       </c>
       <c r="B13" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>128347169</v>
       </c>
       <c r="B14" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>128346963</v>
       </c>
       <c r="B15" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>128346779</v>
       </c>
       <c r="B16" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>128347159</v>
       </c>
       <c r="B17" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>128346773</v>
       </c>
       <c r="B18" t="n">
-        <v>90950</v>
+        <v>90962</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 34528-2025 artfynd.xlsx
+++ b/artfynd/A 34528-2025 artfynd.xlsx
@@ -1868,7 +1868,7 @@
         <v>128346802</v>
       </c>
       <c r="B12" t="n">
-        <v>90962</v>
+        <v>90964</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>128347045</v>
       </c>
       <c r="B13" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>128347169</v>
       </c>
       <c r="B14" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>128346963</v>
       </c>
       <c r="B15" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>128346779</v>
       </c>
       <c r="B16" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>128347159</v>
       </c>
       <c r="B17" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>128346773</v>
       </c>
       <c r="B18" t="n">
-        <v>90962</v>
+        <v>90964</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 34528-2025 artfynd.xlsx
+++ b/artfynd/A 34528-2025 artfynd.xlsx
@@ -1868,7 +1868,7 @@
         <v>128346802</v>
       </c>
       <c r="B12" t="n">
-        <v>90964</v>
+        <v>90965</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>128347045</v>
       </c>
       <c r="B13" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>128346963</v>
       </c>
       <c r="B15" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>128346773</v>
       </c>
       <c r="B18" t="n">
-        <v>90964</v>
+        <v>90965</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 34528-2025 artfynd.xlsx
+++ b/artfynd/A 34528-2025 artfynd.xlsx
@@ -1749,7 +1749,7 @@
         <v>128346968</v>
       </c>
       <c r="B11" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>128346802</v>
       </c>
       <c r="B12" t="n">
-        <v>90965</v>
+        <v>90992</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>128347045</v>
       </c>
       <c r="B13" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>128347169</v>
       </c>
       <c r="B14" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>128346963</v>
       </c>
       <c r="B15" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>128346779</v>
       </c>
       <c r="B16" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>128347159</v>
       </c>
       <c r="B17" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>128346773</v>
       </c>
       <c r="B18" t="n">
-        <v>90965</v>
+        <v>90992</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 34528-2025 artfynd.xlsx
+++ b/artfynd/A 34528-2025 artfynd.xlsx
@@ -1868,7 +1868,7 @@
         <v>128346802</v>
       </c>
       <c r="B12" t="n">
-        <v>90992</v>
+        <v>91002</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>128347045</v>
       </c>
       <c r="B13" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>128347169</v>
       </c>
       <c r="B14" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>128346963</v>
       </c>
       <c r="B15" t="n">
-        <v>92818</v>
+        <v>92830</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>128346779</v>
       </c>
       <c r="B16" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>128347159</v>
       </c>
       <c r="B17" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>128346773</v>
       </c>
       <c r="B18" t="n">
-        <v>90992</v>
+        <v>91002</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 34528-2025 artfynd.xlsx
+++ b/artfynd/A 34528-2025 artfynd.xlsx
@@ -1749,7 +1749,7 @@
         <v>128346968</v>
       </c>
       <c r="B11" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>128346802</v>
       </c>
       <c r="B12" t="n">
-        <v>91002</v>
+        <v>91006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>128347045</v>
       </c>
       <c r="B13" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>128347169</v>
       </c>
       <c r="B14" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>128346963</v>
       </c>
       <c r="B15" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>128346779</v>
       </c>
       <c r="B16" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>128347159</v>
       </c>
       <c r="B17" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>128346773</v>
       </c>
       <c r="B18" t="n">
-        <v>91002</v>
+        <v>91006</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 34528-2025 artfynd.xlsx
+++ b/artfynd/A 34528-2025 artfynd.xlsx
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
@@ -2637,7 +2637,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">

--- a/artfynd/A 34528-2025 artfynd.xlsx
+++ b/artfynd/A 34528-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127814016</v>
+        <v>128064167</v>
       </c>
       <c r="B2" t="n">
-        <v>92778</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -721,13 +721,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698384</v>
+        <v>698438</v>
       </c>
       <c r="R2" t="n">
-        <v>6637232</v>
+        <v>6637253</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,22 +751,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,42 +794,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127813682</v>
+        <v>128064178</v>
       </c>
       <c r="B3" t="n">
-        <v>90950</v>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5745</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gyllenfingersvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria brunneicontusa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -840,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698378</v>
+        <v>698423</v>
       </c>
       <c r="R3" t="n">
-        <v>6637242</v>
+        <v>6637254</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,22 +870,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,42 +913,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127813710</v>
+        <v>128064185</v>
       </c>
       <c r="B4" t="n">
-        <v>90950</v>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5745</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gyllenfingersvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramaria brunneicontusa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698390</v>
+        <v>698427</v>
       </c>
       <c r="R4" t="n">
-        <v>6637234</v>
+        <v>6637261</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,22 +989,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,59 +1032,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127813667</v>
+        <v>128064210</v>
       </c>
       <c r="B5" t="n">
-        <v>90950</v>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5745</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gyllenfingersvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria brunneicontusa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fridhem (Erken) , Upl</t>
+          <t>Fridhem (Erken), Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698380</v>
+        <v>698425</v>
       </c>
       <c r="R5" t="n">
-        <v>6637239</v>
+        <v>6637249</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,22 +1108,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128064167</v>
+        <v>128064221</v>
       </c>
       <c r="B6" t="n">
-        <v>82946</v>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,13 +1197,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698438</v>
+        <v>698433</v>
       </c>
       <c r="R6" t="n">
-        <v>6637253</v>
+        <v>6637241</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128064221</v>
+        <v>128346779</v>
       </c>
       <c r="B7" t="n">
-        <v>82946</v>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,16 +1298,8 @@
           <t>(Nyl.) Rehm</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1316,13 +1308,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698433</v>
+        <v>698383</v>
       </c>
       <c r="R7" t="n">
-        <v>6637241</v>
+        <v>6637243</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1346,22 +1338,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128064178</v>
+        <v>128347159</v>
       </c>
       <c r="B8" t="n">
-        <v>82946</v>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,16 +1409,8 @@
           <t>(Nyl.) Rehm</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1435,13 +1419,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698423</v>
+        <v>698345</v>
       </c>
       <c r="R8" t="n">
-        <v>6637254</v>
+        <v>6637306</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1465,22 +1449,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,10 +1492,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128064210</v>
+        <v>128347165</v>
       </c>
       <c r="B9" t="n">
-        <v>82946</v>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,31 +1520,23 @@
           <t>(Nyl.) Rehm</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fridhem (Erken), Upl</t>
+          <t>Erken, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698425</v>
+        <v>698354</v>
       </c>
       <c r="R9" t="n">
-        <v>6637249</v>
+        <v>6637310</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1584,22 +1560,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1627,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128064185</v>
+        <v>128347169</v>
       </c>
       <c r="B10" t="n">
-        <v>82946</v>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,31 +1631,23 @@
           <t>(Nyl.) Rehm</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fridhem (Erken), Upl</t>
+          <t>Erken , Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698427</v>
+        <v>698346</v>
       </c>
       <c r="R10" t="n">
-        <v>6637261</v>
+        <v>6637297</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1703,22 +1671,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1746,46 +1714,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128346968</v>
+        <v>128347045</v>
       </c>
       <c r="B11" t="n">
-        <v>57717</v>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1793,10 +1752,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698375</v>
+        <v>698345</v>
       </c>
       <c r="R11" t="n">
-        <v>6637261</v>
+        <v>6637238</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1847,6 +1806,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1865,14 +1825,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128346802</v>
+        <v>127813667</v>
       </c>
       <c r="B12" t="n">
-        <v>91006</v>
+        <v>91398</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1895,7 +1855,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1907,14 +1867,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fridhem Erken, Upl</t>
+          <t>Fridhem (Erken) , Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698388</v>
+        <v>698380</v>
       </c>
       <c r="R12" t="n">
-        <v>6637237</v>
+        <v>6637239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,29 +1901,29 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
@@ -1984,48 +1944,56 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128347045</v>
+        <v>127813682</v>
       </c>
       <c r="B13" t="n">
-        <v>92443</v>
+        <v>91398</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>5745</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Erken, Upl</t>
+          <t>Fridhem (Erken), Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698345</v>
+        <v>698378</v>
       </c>
       <c r="R13" t="n">
-        <v>6637238</v>
+        <v>6637242</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2052,22 +2020,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,48 +2063,56 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128347169</v>
+        <v>127813710</v>
       </c>
       <c r="B14" t="n">
-        <v>82983</v>
+        <v>91398</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>5745</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Erken , Upl</t>
+          <t>Fridhem (Erken), Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698346</v>
+        <v>698390</v>
       </c>
       <c r="R14" t="n">
-        <v>6637297</v>
+        <v>6637234</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2163,22 +2139,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2206,48 +2182,56 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128346963</v>
+        <v>128346773</v>
       </c>
       <c r="B15" t="n">
-        <v>92834</v>
+        <v>91398</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>5745</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Erken, Upl</t>
+          <t>Fridhem (Erken), Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698375</v>
+        <v>698383</v>
       </c>
       <c r="R15" t="n">
-        <v>6637261</v>
+        <v>6637243</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2296,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
@@ -2317,48 +2301,56 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128346779</v>
+        <v>128346802</v>
       </c>
       <c r="B16" t="n">
-        <v>82983</v>
+        <v>91398</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>5745</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fridhem (Erken), Upl</t>
+          <t>Fridhem Erken, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698383</v>
+        <v>698388</v>
       </c>
       <c r="R16" t="n">
-        <v>6637243</v>
+        <v>6637237</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2407,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
@@ -2428,48 +2420,56 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128347159</v>
+        <v>128347830</v>
       </c>
       <c r="B17" t="n">
-        <v>82983</v>
+        <v>91398</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>5745</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fridhem (Erken), Upl</t>
+          <t>Fridhem , Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698345</v>
+        <v>698493</v>
       </c>
       <c r="R17" t="n">
-        <v>6637306</v>
+        <v>6637254</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2539,56 +2539,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128346773</v>
+        <v>128346963</v>
       </c>
       <c r="B18" t="n">
-        <v>91006</v>
+        <v>93233</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5745</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gyllenfingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramaria brunneicontusa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fridhem (Erken), Upl</t>
+          <t>Erken, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698383</v>
+        <v>698375</v>
       </c>
       <c r="R18" t="n">
-        <v>6637243</v>
+        <v>6637261</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2637,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
@@ -2655,6 +2647,244 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127814016</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fridhem (Erken), Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>698384</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6637232</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128346968</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Erken, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>698375</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6637261</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34528-2025 artfynd.xlsx
+++ b/artfynd/A 34528-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128064167</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128064178</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128064185</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128064210</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128064221</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1378,6 +1408,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346779</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1489,6 +1524,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347159</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1600,6 +1640,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347165</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1711,6 +1756,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347169</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1822,6 +1872,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347045</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1941,6 +1996,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127813667</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2060,6 +2120,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127813682</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2179,6 +2244,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127813710</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2298,6 +2368,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346773</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2417,6 +2492,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346802</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2536,6 +2616,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128347830</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2647,6 +2732,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346963</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2766,6 +2856,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127814016</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2885,8 +2980,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346968</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>